--- a/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="201">
   <si>
     <t>Result</t>
   </si>
@@ -538,6 +538,111 @@
   </si>
   <si>
     <t>Sat Jul 18 00:04:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:25:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:26:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:27:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:27:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:28:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:29:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:29:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:31:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:31:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:33:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:35:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:36:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:37:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:38:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:38:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:39:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:39:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:41:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:42:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:43:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:43:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:44:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 00:44:46 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1129,7 @@
         <v>52</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>17</v>
@@ -1044,7 +1149,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>18</v>
@@ -1064,7 +1169,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>19</v>
@@ -1084,7 +1189,7 @@
         <v>52</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>20</v>
@@ -1104,7 +1209,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>21</v>
@@ -1124,7 +1229,7 @@
         <v>52</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>32</v>
@@ -1144,7 +1249,7 @@
         <v>52</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>33</v>
@@ -1164,7 +1269,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>22</v>
@@ -1187,7 +1292,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>23</v>
@@ -1210,7 +1315,7 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>24</v>
@@ -1233,7 +1338,7 @@
         <v>52</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>25</v>
@@ -1259,7 +1364,7 @@
         <v>52</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>16</v>
@@ -1294,7 +1399,7 @@
         <v>52</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>28</v>
@@ -1317,7 +1422,7 @@
         <v>52</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>26</v>
@@ -1340,7 +1445,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>27</v>
@@ -1363,7 +1468,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>29</v>
@@ -1386,7 +1491,7 @@
         <v>52</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>30</v>
@@ -1409,7 +1514,7 @@
         <v>52</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>31</v>
@@ -1432,7 +1537,7 @@
         <v>52</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>34</v>
@@ -1455,7 +1560,7 @@
         <v>52</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>35</v>
@@ -1478,7 +1583,7 @@
         <v>52</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>36</v>
@@ -1501,7 +1606,7 @@
         <v>52</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>37</v>
@@ -1524,7 +1629,7 @@
         <v>52</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>38</v>
@@ -1612,7 +1717,7 @@
         <v>52</v>
       </c>
       <c r="B2" t="s" s="8">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>41</v>
@@ -1635,7 +1740,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>42</v>
@@ -1658,7 +1763,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s" s="8">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>43</v>
@@ -1681,7 +1786,7 @@
         <v>52</v>
       </c>
       <c r="B5" t="s" s="8">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>44</v>
@@ -1704,7 +1809,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="s" s="8">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>45</v>
@@ -1727,7 +1832,7 @@
         <v>52</v>
       </c>
       <c r="B7" t="s" s="8">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>46</v>
@@ -1750,7 +1855,7 @@
         <v>52</v>
       </c>
       <c r="B8" t="s" s="8">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>47</v>
@@ -1773,7 +1878,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s" s="8">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>48</v>
@@ -1799,7 +1904,7 @@
         <v>52</v>
       </c>
       <c r="B10" t="s" s="8">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>49</v>
@@ -1825,7 +1930,7 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="8">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>50</v>
@@ -1851,7 +1956,7 @@
         <v>52</v>
       </c>
       <c r="B12" t="s" s="8">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>51</v>
@@ -1968,7 +2073,7 @@
         <v>52</v>
       </c>
       <c r="B4" t="s" s="6">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>100</v>
